--- a/wk3/more_formulas_Excel_Tutorial.xlsx
+++ b/wk3/more_formulas_Excel_Tutorial.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop W11\working_folder\Personales\Upright\Data_Science\instructor-dab-sep-2026\wk3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jatin/Desktop/Learnings/Upright/Student_Repo/wk3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D4D720-E9C4-4A56-AC90-F53B642B78F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A30E82F8-8022-1344-870D-40B688A4EA7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-37800" yWindow="-4580" windowWidth="26200" windowHeight="16840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.PEMDAS" sheetId="9" r:id="rId1"/>
@@ -5228,82 +5228,102 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E471456-9FBA-47D2-9BA4-52D22547D1F7}">
-  <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B3">
+        <f>5*(2+3)</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <f>3*2^2</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="13" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <f>12/3*2</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <f>10-5+2</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="13" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>81</v>
+      </c>
+      <c r="B23">
+        <f>8+(6/2)*3^2-4</f>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -5315,18 +5335,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultColWidth="11.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
     <col min="2" max="2" width="9.33203125" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" customWidth="1"/>
     <col min="7" max="7" width="6.33203125" customWidth="1"/>
     <col min="8" max="8" width="10.33203125" customWidth="1"/>
     <col min="9" max="9" width="6.6640625" customWidth="1"/>
-    <col min="10" max="10" width="4.88671875" customWidth="1"/>
+    <col min="10" max="10" width="4.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="29.4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="33" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>62</v>
       </c>
@@ -5355,7 +5375,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -5365,11 +5385,23 @@
       <c r="C2">
         <v>2</v>
       </c>
+      <c r="D2">
+        <f>B2*C2</f>
+        <v>2400</v>
+      </c>
+      <c r="E2">
+        <f>D2*$I$1</f>
+        <v>360</v>
+      </c>
+      <c r="F2">
+        <f>D2+E2</f>
+        <v>2760</v>
+      </c>
       <c r="K2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -5379,11 +5411,23 @@
       <c r="C3">
         <v>1</v>
       </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D5" si="0">B3*C3</f>
+        <v>300</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E5" si="1">D3*$I$1</f>
+        <v>45</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F5" si="2">D3+E3</f>
+        <v>345</v>
+      </c>
       <c r="K3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>72</v>
       </c>
@@ -5393,11 +5437,23 @@
       <c r="C4">
         <v>4</v>
       </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="2"/>
+        <v>230</v>
+      </c>
       <c r="K4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -5407,21 +5463,33 @@
       <c r="C5">
         <v>10</v>
       </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>250</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="1"/>
+        <v>37.5</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="2"/>
+        <v>287.5</v>
+      </c>
       <c r="K5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K6" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>77</v>
       </c>
@@ -5435,19 +5503,43 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <f>$A11*B$9</f>
+        <v>0.05</v>
+      </c>
+      <c r="C11">
+        <f t="shared" ref="C11:D12" si="3">$A11*C$9</f>
+        <v>0.1</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="3"/>
+        <v>0.15000000000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>0.1</v>
+      </c>
+      <c r="B12">
+        <f>$A12*B$9</f>
+        <v>0.1</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="3"/>
+        <v>0.30000000000000004</v>
       </c>
     </row>
   </sheetData>
@@ -5459,7 +5551,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BC87BE8-7F65-41AA-BE91-22F868F8EA45}">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
     <col min="2" max="3" width="11" customWidth="1"/>
@@ -5471,7 +5563,7 @@
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>62</v>
       </c>
@@ -5497,7 +5589,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -5520,7 +5612,7 @@
         <v>2760</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -5543,7 +5635,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>72</v>
       </c>
@@ -5566,7 +5658,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -5589,12 +5681,12 @@
         <v>287.5</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>77</v>
       </c>
@@ -5608,12 +5700,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>0.05</v>
       </c>
@@ -5630,7 +5722,7 @@
         <v>0.15000000000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>0.1</v>
       </c>
@@ -5655,14 +5747,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.109375" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" customWidth="1"/>
     <col min="4" max="4" width="60" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -5673,7 +5765,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -5684,7 +5776,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -5695,7 +5787,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -5706,7 +5798,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -5714,12 +5806,12 @@
         <v>7200</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D10" s="2" t="s">
         <v>4</v>
       </c>
@@ -5737,7 +5829,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.6640625" customWidth="1"/>
@@ -5745,7 +5837,7 @@
     <col min="6" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -5759,7 +5851,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>101</v>
       </c>
@@ -5773,7 +5865,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>102</v>
       </c>
@@ -5787,7 +5879,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>103</v>
       </c>
@@ -5801,20 +5893,24 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B7" t="str">
+        <f>INDEX(A1:C4,3,2)</f>
+        <v>Bob</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E10" s="2" t="s">
         <v>4</v>
       </c>
@@ -5828,14 +5924,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
@@ -5849,7 +5945,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -5860,7 +5956,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -5868,7 +5964,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -5879,7 +5975,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E10" s="2" t="s">
         <v>4</v>
       </c>
@@ -5893,14 +5989,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -5911,7 +6007,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -5919,7 +6015,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>42</v>
       </c>
@@ -5927,7 +6023,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -5935,7 +6031,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E10" s="2" t="s">
         <v>4</v>
       </c>
@@ -5949,15 +6045,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
@@ -5971,7 +6067,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>49</v>
       </c>
@@ -5982,7 +6078,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>52</v>
       </c>
@@ -5993,7 +6089,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>55</v>
       </c>
@@ -6004,7 +6100,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E10" s="2" t="s">
         <v>4</v>
       </c>
@@ -6018,13 +6114,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>58</v>
       </c>
@@ -6039,7 +6135,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -6050,7 +6146,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -6058,7 +6154,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>60</v>
       </c>
@@ -6066,7 +6162,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>61</v>
       </c>
@@ -6074,12 +6170,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B11" s="4" t="s">
         <v>63</v>
       </c>

--- a/wk3/more_formulas_Excel_Tutorial.xlsx
+++ b/wk3/more_formulas_Excel_Tutorial.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jatin/Desktop/Learnings/Upright/Student_Repo/wk3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A30E82F8-8022-1344-870D-40B688A4EA7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F23F5735-F7C5-4C4B-9B7E-8969C9C2CE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37800" yWindow="-4580" windowWidth="26200" windowHeight="16840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="160" yWindow="660" windowWidth="26200" windowHeight="16840" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.PEMDAS" sheetId="9" r:id="rId1"/>
@@ -23,6 +23,9 @@
     <sheet name="6. CONCATENATE" sheetId="6" r:id="rId8"/>
     <sheet name="7. DSUM" sheetId="7" r:id="rId9"/>
   </sheets>
+  <definedNames>
+    <definedName name="Reginoal_Sales" comment="sales">'2. Named Ranges'!$B$2:$B$5</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,8 +43,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
   <si>
     <t>Price</t>
   </si>
@@ -403,6 +428,12 @@
       </rPr>
       <t xml:space="preserve"> - 4</t>
     </r>
+  </si>
+  <si>
+    <t>Left Side</t>
+  </si>
+  <si>
+    <t>Right Side</t>
   </si>
 </sst>
 </file>
@@ -5815,9 +5846,9 @@
       <c r="D10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E10" t="e">
-        <f>SUM(Regional_Sales)</f>
-        <v>#NAME?</v>
+      <c r="E10">
+        <f>SUM(Reginoal_Sales)</f>
+        <v>23500</v>
       </c>
     </row>
   </sheetData>
@@ -5923,7 +5954,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
@@ -5931,7 +5962,7 @@
     <col min="6" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
@@ -5945,7 +5976,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -5956,7 +5987,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -5964,7 +5995,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -5975,9 +6006,28 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E10" s="2" t="s">
         <v>4</v>
+      </c>
+      <c r="F10" t="str" cm="1">
+        <f t="array" ref="F10:F13">IF(ISBLANK(B1:B4),"Missing Values","Complete")</f>
+        <v>Complete</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F11" t="str">
+        <v>Complete</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F12" t="str">
+        <v>Missing Values</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F13" t="str">
+        <v>Complete</v>
       </c>
     </row>
   </sheetData>
@@ -5988,7 +6038,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
@@ -5996,7 +6046,7 @@
     <col min="6" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -6007,7 +6057,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -6015,7 +6065,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>42</v>
       </c>
@@ -6023,7 +6073,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -6031,9 +6081,45 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F8" t="s">
+        <v>90</v>
+      </c>
+      <c r="G8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E10" s="2" t="s">
         <v>4</v>
+      </c>
+      <c r="F10" t="str">
+        <f>LEFT(A2,3)</f>
+        <v>NYC</v>
+      </c>
+      <c r="G10" t="str">
+        <f>RIGHT(A2,4)</f>
+        <v>9921</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F11" t="str">
+        <f t="shared" ref="F11:F12" si="0">LEFT(A3,3)</f>
+        <v>SFO</v>
+      </c>
+      <c r="G11" t="str">
+        <f t="shared" ref="G11:G12" si="1">RIGHT(A3,4)</f>
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F12" t="str">
+        <f t="shared" si="0"/>
+        <v>LON</v>
+      </c>
+      <c r="G12" t="str">
+        <f t="shared" si="1"/>
+        <v>5542</v>
       </c>
     </row>
   </sheetData>
@@ -6044,7 +6130,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -6053,7 +6139,7 @@
     <col min="6" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
@@ -6067,7 +6153,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>49</v>
       </c>
@@ -6078,7 +6164,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>52</v>
       </c>
@@ -6089,7 +6175,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>55</v>
       </c>
@@ -6100,9 +6186,25 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E10" s="2" t="s">
         <v>4</v>
+      </c>
+      <c r="F10" t="str">
+        <f>_xlfn.CONCAT(A2," ",B2)</f>
+        <v>Jane Doe</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F11" t="str">
+        <f t="shared" ref="F11:F12" si="0">_xlfn.CONCAT(A3," ",B3)</f>
+        <v>John Smith</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F12" t="str">
+        <f t="shared" si="0"/>
+        <v>Alan Turing</v>
       </c>
     </row>
   </sheetData>
@@ -6142,8 +6244,9 @@
       <c r="B2">
         <v>100</v>
       </c>
-      <c r="D2" t="s">
-        <v>60</v>
+      <c r="D2">
+        <f>DSUM(A1:B5,"Sales",E2:E5)</f>
+        <v>530</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
